--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.1.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="59" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.1.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0001.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0001.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -613,19 +613,23 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” = _ =</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]IMAGE EVALUATION</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]IMAGE EVALUATION</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
@@ -661,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -684,24 +688,24 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: è­¦</t>
+          <t>L6: stray/suspicious non-ASCII glyph(s): U+8B66 CJK UNIFIED IDEOGRAPH-8B66 | isolated marker/symbol line :: 警</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Hâ€¢ MAS</t>
+          <t>L14: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: H• MAS</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN, U+00A6 BROKEN BAR | isolated marker/symbol line :: è­¦</t>
+          <t>L6: stray/suspicious non-ASCII glyph(s): U+8B66 CJK UNIFIED IDEOGRAPH-8B66 | isolated marker/symbol line :: 警</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: 6"</t>
+          <t>L12: symbol-only separator/garbage line :: — = _ =</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -743,7 +747,7 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6 â€³</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr"/>
@@ -756,7 +760,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L30: symbol-only separator/garbage line :: (716) 872-4503</t>
+          <t>L19: isolated marker/symbol line :: 6"</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -778,12 +782,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -794,7 +798,7 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: äº¬</t>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+4EAC CJK UNIFIED IDEOGRAPH-4EAC | isolated marker/symbol line :: 京</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr"/>
@@ -805,7 +809,11 @@
           <t>L9: symbol-only separator/garbage line :: 2.8</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr"/>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
+          <t>L30: symbol-only separator/garbage line :: (716) 872-4503</t>
+        </is>
+      </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
@@ -841,7 +849,7 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr"/>
@@ -1049,7 +1057,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1087,12 +1095,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1353,7 +1361,7 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L28: symbol-only separator/garbage line :: (716) 872-4503</t>
+          <t>L22: isolated marker/symbol line :: 6 ″</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1384,7 +1392,7 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "2 F EEE FFEEFEEEE" vs "" :: 2</t>
+          <t>L28: symbol-only separator/garbage line :: (716) 872-4503</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr"/>
@@ -1415,7 +1423,7 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: F</t>
+          <t>L29: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "2 F EEE FFEEFEEEE" vs "" :: 2</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr"/>
@@ -1446,7 +1454,7 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr"/>
@@ -1461,6 +1469,99 @@
       <c r="X21" s="1" t="inlineStr"/>
       <c r="Y21" s="1" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr"/>
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr"/>
+      <c r="D22" s="1" t="inlineStr"/>
+      <c r="E22" s="1" t="inlineStr"/>
+      <c r="F22" s="1" t="inlineStr"/>
+      <c r="G22" s="1" t="inlineStr"/>
+      <c r="H22" s="1" t="inlineStr"/>
+      <c r="I22" s="1" t="inlineStr"/>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
+      <c r="L22" s="1" t="inlineStr"/>
+      <c r="M22" s="1" t="inlineStr"/>
+      <c r="N22" s="1" t="inlineStr">
+        <is>
+          <t>L31: stray/suspicious non-ASCII glyph(s): U+4EAC CJK UNIFIED IDEOGRAPH-4EAC | isolated marker/symbol line :: 京</t>
+        </is>
+      </c>
+      <c r="O22" s="1" t="inlineStr"/>
+      <c r="P22" s="1" t="inlineStr"/>
+      <c r="Q22" s="1" t="inlineStr"/>
+      <c r="R22" s="1" t="inlineStr"/>
+      <c r="S22" s="1" t="inlineStr"/>
+      <c r="T22" s="1" t="inlineStr"/>
+      <c r="U22" s="1" t="inlineStr"/>
+      <c r="V22" s="1" t="inlineStr"/>
+      <c r="W22" s="1" t="inlineStr"/>
+      <c r="X22" s="1" t="inlineStr"/>
+      <c r="Y22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr"/>
+      <c r="D23" s="1" t="inlineStr"/>
+      <c r="E23" s="1" t="inlineStr"/>
+      <c r="F23" s="1" t="inlineStr"/>
+      <c r="G23" s="1" t="inlineStr"/>
+      <c r="H23" s="1" t="inlineStr"/>
+      <c r="I23" s="1" t="inlineStr"/>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
+      <c r="L23" s="1" t="inlineStr"/>
+      <c r="M23" s="1" t="inlineStr"/>
+      <c r="N23" s="1" t="inlineStr">
+        <is>
+          <t>L32: isolated marker/symbol line :: F</t>
+        </is>
+      </c>
+      <c r="O23" s="1" t="inlineStr"/>
+      <c r="P23" s="1" t="inlineStr"/>
+      <c r="Q23" s="1" t="inlineStr"/>
+      <c r="R23" s="1" t="inlineStr"/>
+      <c r="S23" s="1" t="inlineStr"/>
+      <c r="T23" s="1" t="inlineStr"/>
+      <c r="U23" s="1" t="inlineStr"/>
+      <c r="V23" s="1" t="inlineStr"/>
+      <c r="W23" s="1" t="inlineStr"/>
+      <c r="X23" s="1" t="inlineStr"/>
+      <c r="Y23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr"/>
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr"/>
+      <c r="D24" s="1" t="inlineStr"/>
+      <c r="E24" s="1" t="inlineStr"/>
+      <c r="F24" s="1" t="inlineStr"/>
+      <c r="G24" s="1" t="inlineStr"/>
+      <c r="H24" s="1" t="inlineStr"/>
+      <c r="I24" s="1" t="inlineStr"/>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
+      <c r="L24" s="1" t="inlineStr"/>
+      <c r="M24" s="1" t="inlineStr"/>
+      <c r="N24" s="1" t="inlineStr">
+        <is>
+          <t>L35: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O24" s="1" t="inlineStr"/>
+      <c r="P24" s="1" t="inlineStr"/>
+      <c r="Q24" s="1" t="inlineStr"/>
+      <c r="R24" s="1" t="inlineStr"/>
+      <c r="S24" s="1" t="inlineStr"/>
+      <c r="T24" s="1" t="inlineStr"/>
+      <c r="U24" s="1" t="inlineStr"/>
+      <c r="V24" s="1" t="inlineStr"/>
+      <c r="W24" s="1" t="inlineStr"/>
+      <c r="X24" s="1" t="inlineStr"/>
+      <c r="Y24" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
